--- a/移动应用开发大作业评分表.xlsx
+++ b/移动应用开发大作业评分表.xlsx
@@ -253,7 +253,7 @@
     <t>主页面到活动创建页面的跳转：用户可通过主页面上的新增按钮进入活动创建页面，创建完成后自动返回主页面，并看到新建活动已加入展示内容中</t>
   </si>
   <si>
-    <t>主页面到日历页面的跳转：用户可点击主页面中的本周打卡情况区域进入日历页面，从日历页面返回时，应能回到主页面并保持基本浏览状态</t>
+    <t>主页面到日历页面的跳转：用户可点击主页面中日历区域进入日历页面，从日历页面返回时，应能回到主页面并保持基本浏览状态</t>
   </si>
   <si>
     <t>主页面到提醒编辑页面的跳转：用户可点击主页面中的半透明闹铃按钮，进入提醒编辑页面，提醒编辑完成后可返回主页面，整体流程自然清晰</t>
@@ -1885,7 +1885,9 @@
       <c r="C11" s="24">
         <v>3</v>
       </c>
-      <c r="D11" s="15"/>
+      <c r="D11" s="15">
+        <v>1</v>
+      </c>
     </row>
     <row r="12" ht="42" customHeight="1" spans="1:4">
       <c r="A12" s="16"/>
@@ -2246,7 +2248,7 @@
       </c>
       <c r="D48" s="46">
         <f>SUM(D8:D47)</f>
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/移动应用开发大作业评分表.xlsx
+++ b/移动应用开发大作业评分表.xlsx
@@ -1886,7 +1886,7 @@
         <v>3</v>
       </c>
       <c r="D11" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12" ht="42" customHeight="1" spans="1:4">
@@ -1934,7 +1934,7 @@
         <v>3</v>
       </c>
       <c r="D15" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" ht="51" customHeight="1" spans="1:4">
@@ -1967,7 +1967,9 @@
       <c r="C18" s="14">
         <v>3</v>
       </c>
-      <c r="D18" s="15"/>
+      <c r="D18" s="15">
+        <v>3</v>
+      </c>
     </row>
     <row r="19" ht="51" customHeight="1" spans="1:4">
       <c r="A19" s="28"/>
@@ -1989,7 +1991,9 @@
       <c r="C20" s="14">
         <v>4</v>
       </c>
-      <c r="D20" s="15"/>
+      <c r="D20" s="15">
+        <v>4</v>
+      </c>
     </row>
     <row r="21" ht="51" customHeight="1" spans="1:4">
       <c r="A21" s="26"/>
@@ -2059,7 +2063,9 @@
       <c r="C26" s="34">
         <v>2</v>
       </c>
-      <c r="D26" s="34"/>
+      <c r="D26" s="34">
+        <v>2</v>
+      </c>
     </row>
     <row r="27" ht="30" customHeight="1" spans="1:4">
       <c r="A27" s="26"/>
@@ -2248,7 +2254,7 @@
       </c>
       <c r="D48" s="46">
         <f>SUM(D8:D47)</f>
-        <v>22</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>

--- a/移动应用开发大作业评分表.xlsx
+++ b/移动应用开发大作业评分表.xlsx
@@ -195,7 +195,7 @@
     <t>启动页面：启动应用时展示 App Logo。</t>
   </si>
   <si>
-    <t xml:space="preserve">主页面：默认采用卡片式展示已创建活动，支持卡片模式和列表模式两种显示方式，均能清晰展示活动名称、本周打卡情况、累计打卡天数等关键信息，卡片模式下，可额外展示本周打卡情况、详细记录等信息
+    <t xml:space="preserve">主页面：默认采用卡片式展示已创建活动，支持卡片模式和列表模式两种显示方式，均能清晰展示活动名称、本日打卡情况、累计打卡天数等关键信息，卡片模式下，可额外展示本周打卡情况、详细记录等信息
 </t>
   </si>
   <si>
@@ -353,7 +353,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="33">
+  <fonts count="35">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -422,14 +422,22 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Times New Roman"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
     </font>
     <font>
       <sz val="11"/>
@@ -583,6 +591,12 @@
     <font>
       <b/>
       <sz val="20"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="0"/>
@@ -1151,137 +1165,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="21" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="21" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="22" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="23" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="24" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="4" borderId="23" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="5" borderId="25" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="26" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="21" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="22" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="23" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="24" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="23" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="5" borderId="25" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="26" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1322,40 +1336,37 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1364,7 +1375,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1376,19 +1387,16 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1397,32 +1405,29 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1868,7 +1873,7 @@
         <v>4</v>
       </c>
       <c r="D9" s="19">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10" ht="42" customHeight="1" spans="1:4">
@@ -1882,7 +1887,7 @@
       <c r="B11" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="24">
+      <c r="C11" s="21">
         <v>3</v>
       </c>
       <c r="D11" s="15">
@@ -1894,17 +1899,17 @@
       <c r="B12" s="23" t="s">
         <v>16</v>
       </c>
-      <c r="C12" s="24">
+      <c r="C12" s="21">
         <v>1</v>
       </c>
       <c r="D12" s="15"/>
     </row>
     <row r="13" ht="42" customHeight="1" spans="1:4">
-      <c r="A13" s="25"/>
+      <c r="A13" s="24"/>
       <c r="B13" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="C13" s="24">
+      <c r="C13" s="21">
         <v>1</v>
       </c>
       <c r="D13" s="15">
@@ -1912,10 +1917,10 @@
       </c>
     </row>
     <row r="14" ht="51" customHeight="1" spans="1:4">
-      <c r="A14" s="26" t="s">
+      <c r="A14" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="B14" s="27" t="s">
+      <c r="B14" s="26" t="s">
         <v>19</v>
       </c>
       <c r="C14" s="14">
@@ -1926,20 +1931,20 @@
       </c>
     </row>
     <row r="15" ht="51" customHeight="1" spans="1:4">
-      <c r="A15" s="28"/>
-      <c r="B15" s="27" t="s">
+      <c r="A15" s="27"/>
+      <c r="B15" s="26" t="s">
         <v>20</v>
       </c>
       <c r="C15" s="14">
         <v>3</v>
       </c>
       <c r="D15" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16" ht="51" customHeight="1" spans="1:4">
-      <c r="A16" s="28"/>
-      <c r="B16" s="29" t="s">
+      <c r="A16" s="27"/>
+      <c r="B16" s="28" t="s">
         <v>21</v>
       </c>
       <c r="C16" s="14">
@@ -1950,18 +1955,20 @@
       </c>
     </row>
     <row r="17" ht="51" customHeight="1" spans="1:4">
-      <c r="A17" s="28"/>
-      <c r="B17" s="29" t="s">
+      <c r="A17" s="27"/>
+      <c r="B17" s="28" t="s">
         <v>22</v>
       </c>
       <c r="C17" s="14">
         <v>4</v>
       </c>
-      <c r="D17" s="15"/>
+      <c r="D17" s="15">
+        <v>4</v>
+      </c>
     </row>
     <row r="18" ht="51" customHeight="1" spans="1:4">
-      <c r="A18" s="28"/>
-      <c r="B18" s="29" t="s">
+      <c r="A18" s="27"/>
+      <c r="B18" s="28" t="s">
         <v>23</v>
       </c>
       <c r="C18" s="14">
@@ -1972,8 +1979,8 @@
       </c>
     </row>
     <row r="19" ht="51" customHeight="1" spans="1:4">
-      <c r="A19" s="28"/>
-      <c r="B19" s="29" t="s">
+      <c r="A19" s="27"/>
+      <c r="B19" s="28" t="s">
         <v>24</v>
       </c>
       <c r="C19" s="14">
@@ -1982,10 +1989,10 @@
       <c r="D19" s="15"/>
     </row>
     <row r="20" ht="51" customHeight="1" spans="1:4">
-      <c r="A20" s="26" t="s">
+      <c r="A20" s="25" t="s">
         <v>25</v>
       </c>
-      <c r="B20" s="29" t="s">
+      <c r="B20" s="28" t="s">
         <v>26</v>
       </c>
       <c r="C20" s="14">
@@ -1996,8 +2003,8 @@
       </c>
     </row>
     <row r="21" ht="51" customHeight="1" spans="1:4">
-      <c r="A21" s="26"/>
-      <c r="B21" s="29" t="s">
+      <c r="A21" s="25"/>
+      <c r="B21" s="28" t="s">
         <v>27</v>
       </c>
       <c r="C21" s="14">
@@ -2008,20 +2015,20 @@
       </c>
     </row>
     <row r="22" ht="48" customHeight="1" spans="1:4">
-      <c r="A22" s="30"/>
-      <c r="B22" s="31" t="s">
+      <c r="A22" s="29"/>
+      <c r="B22" s="30" t="s">
         <v>28</v>
       </c>
-      <c r="C22" s="32">
+      <c r="C22" s="14">
         <v>3</v>
       </c>
       <c r="D22" s="15"/>
     </row>
     <row r="23" ht="50" customHeight="1" spans="1:4">
-      <c r="A23" s="26" t="s">
+      <c r="A23" s="25" t="s">
         <v>29</v>
       </c>
-      <c r="B23" s="27" t="s">
+      <c r="B23" s="26" t="s">
         <v>30</v>
       </c>
       <c r="C23" s="14">
@@ -2032,8 +2039,8 @@
       </c>
     </row>
     <row r="24" ht="48" customHeight="1" spans="1:4">
-      <c r="A24" s="26"/>
-      <c r="B24" s="27" t="s">
+      <c r="A24" s="25"/>
+      <c r="B24" s="26" t="s">
         <v>31</v>
       </c>
       <c r="C24" s="14">
@@ -2044,217 +2051,217 @@
       </c>
     </row>
     <row r="25" ht="30" customHeight="1" spans="1:4">
-      <c r="A25" s="26"/>
-      <c r="B25" s="33" t="s">
+      <c r="A25" s="25"/>
+      <c r="B25" s="31" t="s">
         <v>32</v>
       </c>
-      <c r="C25" s="34">
+      <c r="C25" s="32">
         <v>2</v>
       </c>
-      <c r="D25" s="34">
+      <c r="D25" s="32">
         <v>2</v>
       </c>
     </row>
     <row r="26" ht="30" customHeight="1" spans="1:4">
-      <c r="A26" s="26"/>
-      <c r="B26" s="33" t="s">
+      <c r="A26" s="25"/>
+      <c r="B26" s="31" t="s">
         <v>33</v>
       </c>
-      <c r="C26" s="34">
+      <c r="C26" s="32">
         <v>2</v>
       </c>
-      <c r="D26" s="34">
+      <c r="D26" s="32">
         <v>2</v>
       </c>
     </row>
     <row r="27" ht="30" customHeight="1" spans="1:4">
-      <c r="A27" s="26"/>
-      <c r="B27" s="33" t="s">
+      <c r="A27" s="25"/>
+      <c r="B27" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="34">
+      <c r="C27" s="32">
         <v>2</v>
       </c>
-      <c r="D27" s="34"/>
+      <c r="D27" s="32"/>
     </row>
     <row r="28" ht="30" customHeight="1" spans="1:4">
-      <c r="A28" s="26"/>
-      <c r="B28" s="33" t="s">
+      <c r="A28" s="25"/>
+      <c r="B28" s="31" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="34">
+      <c r="C28" s="32">
         <v>4</v>
       </c>
-      <c r="D28" s="34"/>
+      <c r="D28" s="32"/>
     </row>
     <row r="29" ht="30" customHeight="1" spans="1:4">
-      <c r="A29" s="26"/>
-      <c r="B29" s="33" t="s">
+      <c r="A29" s="25"/>
+      <c r="B29" s="31" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="34">
+      <c r="C29" s="32">
         <v>3</v>
       </c>
-      <c r="D29" s="34"/>
+      <c r="D29" s="32"/>
     </row>
     <row r="30" ht="30" customHeight="1" spans="1:4">
-      <c r="A30" s="26"/>
-      <c r="B30" s="33" t="s">
+      <c r="A30" s="25"/>
+      <c r="B30" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="34">
+      <c r="C30" s="32">
         <v>2</v>
       </c>
-      <c r="D30" s="34"/>
+      <c r="D30" s="32"/>
     </row>
     <row r="31" ht="30" customHeight="1" spans="1:4">
-      <c r="A31" s="35" t="s">
+      <c r="A31" s="33" t="s">
         <v>38</v>
       </c>
-      <c r="B31" s="33" t="s">
+      <c r="B31" s="31" t="s">
         <v>39</v>
       </c>
-      <c r="C31" s="34">
+      <c r="C31" s="32">
         <v>10</v>
       </c>
-      <c r="D31" s="34"/>
+      <c r="D31" s="32"/>
     </row>
     <row r="32" ht="30" customHeight="1" spans="1:4">
-      <c r="A32" s="36" t="s">
+      <c r="A32" s="34" t="s">
         <v>40</v>
       </c>
-      <c r="B32" s="33" t="s">
+      <c r="B32" s="31" t="s">
         <v>41</v>
       </c>
-      <c r="C32" s="34">
+      <c r="C32" s="32">
         <v>10</v>
       </c>
-      <c r="D32" s="34"/>
+      <c r="D32" s="32"/>
     </row>
     <row r="33" ht="27" customHeight="1" spans="1:4">
-      <c r="A33" s="36"/>
-      <c r="B33" s="33" t="s">
+      <c r="A33" s="34"/>
+      <c r="B33" s="31" t="s">
         <v>42</v>
       </c>
-      <c r="C33" s="34">
+      <c r="C33" s="32">
         <v>10</v>
       </c>
-      <c r="D33" s="34"/>
+      <c r="D33" s="32"/>
     </row>
     <row r="34" ht="40" customHeight="1" spans="1:4">
-      <c r="A34" s="36"/>
-      <c r="B34" s="33" t="s">
+      <c r="A34" s="34"/>
+      <c r="B34" s="31" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="34">
+      <c r="C34" s="32">
         <v>10</v>
       </c>
-      <c r="D34" s="34"/>
+      <c r="D34" s="32"/>
     </row>
     <row r="35" spans="1:4">
-      <c r="A35" s="37" t="s">
+      <c r="A35" s="35" t="s">
         <v>44</v>
       </c>
-      <c r="B35" s="38" t="s">
+      <c r="B35" s="36" t="s">
         <v>45</v>
       </c>
-      <c r="C35" s="39">
+      <c r="C35" s="19">
         <v>4</v>
       </c>
-      <c r="D35" s="39"/>
+      <c r="D35" s="19"/>
     </row>
     <row r="36" spans="1:4">
-      <c r="A36" s="40"/>
-      <c r="B36" s="41"/>
-      <c r="C36" s="42"/>
-      <c r="D36" s="42"/>
+      <c r="A36" s="37"/>
+      <c r="B36" s="38"/>
+      <c r="C36" s="39"/>
+      <c r="D36" s="39"/>
     </row>
     <row r="37" spans="1:4">
-      <c r="A37" s="40"/>
-      <c r="B37" s="41"/>
-      <c r="C37" s="42"/>
-      <c r="D37" s="42"/>
+      <c r="A37" s="37"/>
+      <c r="B37" s="38"/>
+      <c r="C37" s="39"/>
+      <c r="D37" s="39"/>
     </row>
     <row r="38" spans="1:4">
-      <c r="A38" s="40"/>
-      <c r="B38" s="41"/>
-      <c r="C38" s="42"/>
-      <c r="D38" s="42"/>
+      <c r="A38" s="37"/>
+      <c r="B38" s="38"/>
+      <c r="C38" s="39"/>
+      <c r="D38" s="39"/>
     </row>
     <row r="39" spans="1:4">
-      <c r="A39" s="40"/>
-      <c r="B39" s="41"/>
-      <c r="C39" s="42"/>
-      <c r="D39" s="42"/>
+      <c r="A39" s="37"/>
+      <c r="B39" s="38"/>
+      <c r="C39" s="39"/>
+      <c r="D39" s="39"/>
     </row>
     <row r="40" spans="1:4">
-      <c r="A40" s="40"/>
-      <c r="B40" s="38" t="s">
+      <c r="A40" s="37"/>
+      <c r="B40" s="36" t="s">
         <v>46</v>
       </c>
-      <c r="C40" s="39">
+      <c r="C40" s="19">
         <v>3</v>
       </c>
-      <c r="D40" s="39"/>
+      <c r="D40" s="19"/>
     </row>
     <row r="41" spans="1:4">
-      <c r="A41" s="40"/>
-      <c r="B41" s="41"/>
-      <c r="C41" s="42"/>
-      <c r="D41" s="42"/>
+      <c r="A41" s="37"/>
+      <c r="B41" s="38"/>
+      <c r="C41" s="39"/>
+      <c r="D41" s="39"/>
     </row>
     <row r="42" spans="1:4">
-      <c r="A42" s="40"/>
-      <c r="B42" s="41"/>
-      <c r="C42" s="42"/>
-      <c r="D42" s="42"/>
+      <c r="A42" s="37"/>
+      <c r="B42" s="38"/>
+      <c r="C42" s="39"/>
+      <c r="D42" s="39"/>
     </row>
     <row r="43" ht="25" customHeight="1" spans="1:4">
-      <c r="A43" s="40"/>
-      <c r="B43" s="41"/>
-      <c r="C43" s="42"/>
-      <c r="D43" s="42"/>
+      <c r="A43" s="37"/>
+      <c r="B43" s="38"/>
+      <c r="C43" s="39"/>
+      <c r="D43" s="39"/>
     </row>
     <row r="44" ht="25" customHeight="1" spans="1:4">
-      <c r="A44" s="40"/>
-      <c r="B44" s="41"/>
-      <c r="C44" s="42"/>
-      <c r="D44" s="42"/>
+      <c r="A44" s="37"/>
+      <c r="B44" s="38"/>
+      <c r="C44" s="39"/>
+      <c r="D44" s="39"/>
     </row>
     <row r="45" ht="25" customHeight="1" spans="1:4">
-      <c r="A45" s="40"/>
-      <c r="B45" s="41" t="s">
+      <c r="A45" s="37"/>
+      <c r="B45" s="38" t="s">
         <v>47</v>
       </c>
-      <c r="C45" s="43">
+      <c r="C45" s="40">
         <v>3</v>
       </c>
-      <c r="D45" s="44"/>
+      <c r="D45" s="39"/>
     </row>
     <row r="46" ht="25" customHeight="1" spans="1:4">
-      <c r="A46" s="40"/>
-      <c r="B46" s="41"/>
-      <c r="C46" s="43"/>
-      <c r="D46" s="44"/>
+      <c r="A46" s="37"/>
+      <c r="B46" s="38"/>
+      <c r="C46" s="40"/>
+      <c r="D46" s="39"/>
     </row>
     <row r="47" ht="25" customHeight="1" spans="1:4">
-      <c r="A47" s="40"/>
-      <c r="B47" s="41"/>
-      <c r="C47" s="43"/>
-      <c r="D47" s="44"/>
+      <c r="A47" s="37"/>
+      <c r="B47" s="38"/>
+      <c r="C47" s="40"/>
+      <c r="D47" s="39"/>
     </row>
     <row r="48" ht="25" customHeight="1" spans="1:4">
-      <c r="A48" s="45" t="s">
+      <c r="A48" s="41" t="s">
         <v>48</v>
       </c>
-      <c r="B48" s="46"/>
-      <c r="C48" s="47">
+      <c r="B48" s="42"/>
+      <c r="C48" s="43">
         <f>SUM(C8:C34)</f>
         <v>100</v>
       </c>
-      <c r="D48" s="46">
+      <c r="D48" s="44">
         <f>SUM(D8:D47)</f>
-        <v>34</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
